--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131989685</v>
       </c>
       <c r="B2" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131989734</v>
       </c>
       <c r="B3" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,42 +898,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131989726</v>
+        <v>131989698</v>
       </c>
       <c r="B4" t="n">
-        <v>99046</v>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566577</v>
+        <v>566601</v>
       </c>
       <c r="R4" t="n">
-        <v>6679273</v>
+        <v>6679232</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,50 +1010,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131989698</v>
+        <v>131989697</v>
       </c>
       <c r="B5" t="n">
-        <v>4774</v>
+        <v>91841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566601</v>
+        <v>566627</v>
       </c>
       <c r="R5" t="n">
-        <v>6679232</v>
+        <v>6679348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,45 +1117,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131989697</v>
+        <v>131989726</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>99047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566627</v>
+        <v>566577</v>
       </c>
       <c r="R6" t="n">
-        <v>6679348</v>
+        <v>6679273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,54 +1233,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131989730</v>
+        <v>131989688</v>
       </c>
       <c r="B7" t="n">
-        <v>99046</v>
+        <v>91804</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566655</v>
+        <v>566662</v>
       </c>
       <c r="R7" t="n">
-        <v>6679324</v>
+        <v>6679349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1343,7 @@
         <v>131989716</v>
       </c>
       <c r="B8" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,45 +1456,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131989688</v>
+        <v>131989730</v>
       </c>
       <c r="B9" t="n">
-        <v>91803</v>
+        <v>99047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566662</v>
+        <v>566655</v>
       </c>
       <c r="R9" t="n">
-        <v>6679349</v>
+        <v>6679324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>131989728</v>
       </c>
       <c r="B10" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>131989719</v>
       </c>
       <c r="B11" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,42 +1804,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989712</v>
+        <v>131989703</v>
       </c>
       <c r="B12" t="n">
-        <v>99046</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1848,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566598</v>
+        <v>566786</v>
       </c>
       <c r="R12" t="n">
-        <v>6679291</v>
+        <v>6679271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,38 +1916,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989703</v>
+        <v>131989712</v>
       </c>
       <c r="B13" t="n">
-        <v>57903</v>
+        <v>99047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566786</v>
+        <v>566598</v>
       </c>
       <c r="R13" t="n">
-        <v>6679271</v>
+        <v>6679291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,7 +2035,7 @@
         <v>131989718</v>
       </c>
       <c r="B14" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,54 +2148,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131989731</v>
+        <v>131989696</v>
       </c>
       <c r="B15" t="n">
-        <v>99046</v>
+        <v>91841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566563</v>
+        <v>566485</v>
       </c>
       <c r="R15" t="n">
-        <v>6679314</v>
+        <v>6679257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,7 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,7 +2258,7 @@
         <v>131989715</v>
       </c>
       <c r="B16" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,45 +2371,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131989696</v>
+        <v>131989720</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>99047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566485</v>
+        <v>566600</v>
       </c>
       <c r="R17" t="n">
-        <v>6679257</v>
+        <v>6679228</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131989720</v>
+        <v>131989731</v>
       </c>
       <c r="B18" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566600</v>
+        <v>566563</v>
       </c>
       <c r="R18" t="n">
-        <v>6679228</v>
+        <v>6679314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,7 +2606,7 @@
         <v>131989689</v>
       </c>
       <c r="B19" t="n">
-        <v>92212</v>
+        <v>92213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131989735</v>
+        <v>131989722</v>
       </c>
       <c r="B20" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566580</v>
+        <v>566570</v>
       </c>
       <c r="R20" t="n">
-        <v>6679241</v>
+        <v>6679277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131989722</v>
+        <v>131989735</v>
       </c>
       <c r="B21" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566570</v>
+        <v>566580</v>
       </c>
       <c r="R21" t="n">
-        <v>6679277</v>
+        <v>6679241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,7 +2945,7 @@
         <v>131989742</v>
       </c>
       <c r="B22" t="n">
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,38 +3054,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989701</v>
+        <v>131989725</v>
       </c>
       <c r="B23" t="n">
-        <v>58065</v>
+        <v>99047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3094,10 +3098,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566614</v>
+        <v>566869</v>
       </c>
       <c r="R23" t="n">
-        <v>6679286</v>
+        <v>6679157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3129,7 +3133,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3139,7 +3143,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3166,42 +3170,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989725</v>
+        <v>131989700</v>
       </c>
       <c r="B24" t="n">
-        <v>99046</v>
+        <v>58066</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3210,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566869</v>
+        <v>566496</v>
       </c>
       <c r="R24" t="n">
-        <v>6679157</v>
+        <v>6679281</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3245,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3255,7 +3260,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,10 +3287,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989700</v>
+        <v>131989701</v>
       </c>
       <c r="B25" t="n">
-        <v>58065</v>
+        <v>58066</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,11 +3316,6 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566496</v>
+        <v>566614</v>
       </c>
       <c r="R25" t="n">
-        <v>6679281</v>
+        <v>6679286</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,7 +3402,7 @@
         <v>131989686</v>
       </c>
       <c r="B26" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989687</v>
+        <v>131989691</v>
       </c>
       <c r="B27" t="n">
-        <v>91803</v>
+        <v>91841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566505</v>
+        <v>566556</v>
       </c>
       <c r="R27" t="n">
-        <v>6679080</v>
+        <v>6679090</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,54 +3613,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989717</v>
+        <v>131989687</v>
       </c>
       <c r="B28" t="n">
-        <v>99046</v>
+        <v>91804</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566525</v>
+        <v>566505</v>
       </c>
       <c r="R28" t="n">
-        <v>6679095</v>
+        <v>6679080</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3692,7 +3683,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3693,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,45 +3720,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989691</v>
+        <v>131989717</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>99047</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566556</v>
+        <v>566525</v>
       </c>
       <c r="R29" t="n">
-        <v>6679090</v>
+        <v>6679095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,7 +3839,7 @@
         <v>131989713</v>
       </c>
       <c r="B30" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>131989709</v>
       </c>
       <c r="B31" t="n">
-        <v>97911</v>
+        <v>97912</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131989710</v>
       </c>
       <c r="B32" t="n">
-        <v>97911</v>
+        <v>97912</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>131989690</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4278,10 +4278,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989729</v>
+        <v>131989714</v>
       </c>
       <c r="B34" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4316,16 +4316,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566608</v>
+        <v>566771</v>
       </c>
       <c r="R34" t="n">
-        <v>6679223</v>
+        <v>6679247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4357,7 +4362,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4367,7 +4372,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4394,10 +4399,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989714</v>
+        <v>131989729</v>
       </c>
       <c r="B35" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4424,7 +4429,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4432,21 +4437,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566771</v>
+        <v>566608</v>
       </c>
       <c r="R35" t="n">
-        <v>6679247</v>
+        <v>6679223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,7 +4518,7 @@
         <v>131989744</v>
       </c>
       <c r="B36" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>131989732</v>
       </c>
       <c r="B37" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131989693</v>
+        <v>131989695</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566484</v>
+        <v>566461</v>
       </c>
       <c r="R38" t="n">
-        <v>6679089</v>
+        <v>6679189</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4853,7 +4853,7 @@
         <v>131989692</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131989695</v>
+        <v>131989693</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566461</v>
+        <v>566484</v>
       </c>
       <c r="R40" t="n">
-        <v>6679189</v>
+        <v>6679089</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5067,7 +5067,7 @@
         <v>131989721</v>
       </c>
       <c r="B41" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>131989724</v>
       </c>
       <c r="B42" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>131989743</v>
       </c>
       <c r="B43" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131989685</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131989734</v>
       </c>
       <c r="B3" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,38 +898,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131989698</v>
+        <v>131989726</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>99052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566601</v>
+        <v>566577</v>
       </c>
       <c r="R4" t="n">
-        <v>6679232</v>
+        <v>6679273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1017,7 @@
         <v>131989697</v>
       </c>
       <c r="B5" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,42 +1121,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131989726</v>
+        <v>131989698</v>
       </c>
       <c r="B6" t="n">
-        <v>99047</v>
+        <v>4775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566577</v>
+        <v>566601</v>
       </c>
       <c r="R6" t="n">
-        <v>6679273</v>
+        <v>6679232</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1236,7 @@
         <v>131989688</v>
       </c>
       <c r="B7" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>131989716</v>
       </c>
       <c r="B8" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131989730</v>
       </c>
       <c r="B9" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>131989728</v>
       </c>
       <c r="B10" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>131989719</v>
       </c>
       <c r="B11" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>131989703</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>131989712</v>
       </c>
       <c r="B13" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>131989718</v>
       </c>
       <c r="B14" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>131989696</v>
       </c>
       <c r="B15" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>131989715</v>
       </c>
       <c r="B16" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>131989720</v>
       </c>
       <c r="B17" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>131989731</v>
       </c>
       <c r="B18" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131989689</v>
+        <v>131989722</v>
       </c>
       <c r="B19" t="n">
-        <v>92213</v>
+        <v>99052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,34 +2614,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566483</v>
+        <v>566570</v>
       </c>
       <c r="R19" t="n">
-        <v>6679261</v>
+        <v>6679277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2682,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,7 +2692,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,10 +2719,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131989722</v>
+        <v>131989735</v>
       </c>
       <c r="B20" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2749,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2754,10 +2763,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566570</v>
+        <v>566580</v>
       </c>
       <c r="R20" t="n">
-        <v>6679277</v>
+        <v>6679241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,7 +2798,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2799,7 +2808,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,10 +2835,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131989735</v>
+        <v>131989689</v>
       </c>
       <c r="B21" t="n">
-        <v>99047</v>
+        <v>92218</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,43 +2846,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566580</v>
+        <v>566483</v>
       </c>
       <c r="R21" t="n">
-        <v>6679241</v>
+        <v>6679261</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,38 +2942,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131989742</v>
+        <v>131989700</v>
       </c>
       <c r="B22" t="n">
-        <v>8444</v>
+        <v>58071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566722</v>
+        <v>566496</v>
       </c>
       <c r="R22" t="n">
-        <v>6679268</v>
+        <v>6679281</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3022,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3027,7 +3032,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,42 +3059,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989725</v>
+        <v>131989701</v>
       </c>
       <c r="B23" t="n">
-        <v>99047</v>
+        <v>58071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3098,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566869</v>
+        <v>566614</v>
       </c>
       <c r="R23" t="n">
-        <v>6679157</v>
+        <v>6679286</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3133,7 +3134,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3143,7 +3144,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,43 +3171,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989700</v>
+        <v>131989742</v>
       </c>
       <c r="B24" t="n">
-        <v>58066</v>
+        <v>8444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3215,10 +3211,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566496</v>
+        <v>566722</v>
       </c>
       <c r="R24" t="n">
-        <v>6679281</v>
+        <v>6679268</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,7 +3256,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,38 +3283,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989701</v>
+        <v>131989725</v>
       </c>
       <c r="B25" t="n">
-        <v>58066</v>
+        <v>99052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566614</v>
+        <v>566869</v>
       </c>
       <c r="R25" t="n">
-        <v>6679286</v>
+        <v>6679157</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,7 +3402,7 @@
         <v>131989686</v>
       </c>
       <c r="B26" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,45 +3506,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989691</v>
+        <v>131989717</v>
       </c>
       <c r="B27" t="n">
-        <v>91841</v>
+        <v>99052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566556</v>
+        <v>566525</v>
       </c>
       <c r="R27" t="n">
-        <v>6679090</v>
+        <v>6679095</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,32 +3622,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989687</v>
+        <v>131989691</v>
       </c>
       <c r="B28" t="n">
-        <v>91804</v>
+        <v>91846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3648,10 +3657,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566505</v>
+        <v>566556</v>
       </c>
       <c r="R28" t="n">
-        <v>6679080</v>
+        <v>6679090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3683,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3693,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3720,54 +3729,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989717</v>
+        <v>131989687</v>
       </c>
       <c r="B29" t="n">
-        <v>99047</v>
+        <v>91809</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566525</v>
+        <v>566505</v>
       </c>
       <c r="R29" t="n">
-        <v>6679095</v>
+        <v>6679080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,7 +3839,7 @@
         <v>131989713</v>
       </c>
       <c r="B30" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>131989709</v>
       </c>
       <c r="B31" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131989710</v>
       </c>
       <c r="B32" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>131989690</v>
       </c>
       <c r="B33" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4278,47 +4278,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989714</v>
+        <v>131989744</v>
       </c>
       <c r="B34" t="n">
-        <v>99047</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4327,10 +4318,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566771</v>
+        <v>566439</v>
       </c>
       <c r="R34" t="n">
-        <v>6679247</v>
+        <v>6679145</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4362,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4372,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,10 +4390,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989729</v>
+        <v>131989714</v>
       </c>
       <c r="B35" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4420,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4437,16 +4428,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566608</v>
+        <v>566771</v>
       </c>
       <c r="R35" t="n">
-        <v>6679223</v>
+        <v>6679247</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4474,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4484,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,38 +4511,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989744</v>
+        <v>131989729</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>99052</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566439</v>
+        <v>566608</v>
       </c>
       <c r="R36" t="n">
-        <v>6679145</v>
+        <v>6679223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,7 +4630,7 @@
         <v>131989732</v>
       </c>
       <c r="B37" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>131989695</v>
       </c>
       <c r="B38" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>131989692</v>
       </c>
       <c r="B39" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>131989693</v>
       </c>
       <c r="B40" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>131989721</v>
       </c>
       <c r="B41" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5180,42 +5180,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131989724</v>
+        <v>131989743</v>
       </c>
       <c r="B42" t="n">
-        <v>99047</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5224,10 +5220,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566527</v>
+        <v>566470</v>
       </c>
       <c r="R42" t="n">
-        <v>6679247</v>
+        <v>6679099</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5259,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5269,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5296,38 +5292,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131989743</v>
+        <v>131989724</v>
       </c>
       <c r="B43" t="n">
-        <v>5179</v>
+        <v>99052</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566470</v>
+        <v>566527</v>
       </c>
       <c r="R43" t="n">
-        <v>6679099</v>
+        <v>6679247</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -3952,32 +3952,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131989709</v>
+        <v>131989690</v>
       </c>
       <c r="B31" t="n">
-        <v>97917</v>
+        <v>91846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566652</v>
+        <v>566533</v>
       </c>
       <c r="R31" t="n">
-        <v>6679329</v>
+        <v>6679097</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,12 +4032,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>I gammal kolbotten</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131989710</v>
+        <v>131989709</v>
       </c>
       <c r="B32" t="n">
         <v>97917</v>
@@ -4099,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566626</v>
+        <v>566652</v>
       </c>
       <c r="R32" t="n">
-        <v>6679348</v>
+        <v>6679329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4134,7 +4129,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4144,7 +4139,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>I gammal kolbotten</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,32 +4171,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131989690</v>
+        <v>131989710</v>
       </c>
       <c r="B33" t="n">
-        <v>91846</v>
+        <v>97917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566533</v>
+        <v>566626</v>
       </c>
       <c r="R33" t="n">
-        <v>6679097</v>
+        <v>6679348</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131989685</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131989734</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131989697</v>
       </c>
       <c r="B4" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131989726</v>
       </c>
       <c r="B6" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,54 +1233,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131989716</v>
+        <v>131989688</v>
       </c>
       <c r="B7" t="n">
-        <v>99095</v>
+        <v>91855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566574</v>
+        <v>566662</v>
       </c>
       <c r="R7" t="n">
-        <v>6679277</v>
+        <v>6679349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,45 +1340,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131989688</v>
+        <v>131989716</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566662</v>
+        <v>566574</v>
       </c>
       <c r="R8" t="n">
-        <v>6679349</v>
+        <v>6679277</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
         <v>131989730</v>
       </c>
       <c r="B9" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>131989728</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>131989719</v>
       </c>
       <c r="B11" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,38 +1804,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989703</v>
+        <v>131989712</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1844,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566786</v>
+        <v>566598</v>
       </c>
       <c r="R12" t="n">
-        <v>6679271</v>
+        <v>6679291</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989712</v>
+        <v>131989718</v>
       </c>
       <c r="B13" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,7 +1950,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1960,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566598</v>
+        <v>566526</v>
       </c>
       <c r="R13" t="n">
-        <v>6679291</v>
+        <v>6679221</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1999,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2009,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,42 +2036,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989718</v>
+        <v>131989703</v>
       </c>
       <c r="B14" t="n">
-        <v>99095</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566526</v>
+        <v>566786</v>
       </c>
       <c r="R14" t="n">
-        <v>6679221</v>
+        <v>6679271</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,54 +2148,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131989715</v>
+        <v>131989696</v>
       </c>
       <c r="B15" t="n">
-        <v>99095</v>
+        <v>91892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566602</v>
+        <v>566485</v>
       </c>
       <c r="R15" t="n">
-        <v>6679219</v>
+        <v>6679257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,7 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131989720</v>
+        <v>131989715</v>
       </c>
       <c r="B16" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,7 +2285,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2308,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566600</v>
+        <v>566602</v>
       </c>
       <c r="R16" t="n">
-        <v>6679228</v>
+        <v>6679219</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2344,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131989731</v>
+        <v>131989720</v>
       </c>
       <c r="B17" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2401,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2424,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566563</v>
+        <v>566600</v>
       </c>
       <c r="R17" t="n">
-        <v>6679314</v>
+        <v>6679228</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,45 +2487,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131989696</v>
+        <v>131989731</v>
       </c>
       <c r="B18" t="n">
-        <v>91889</v>
+        <v>99098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566485</v>
+        <v>566563</v>
       </c>
       <c r="R18" t="n">
-        <v>6679257</v>
+        <v>6679314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,7 +2606,7 @@
         <v>131989689</v>
       </c>
       <c r="B19" t="n">
-        <v>92261</v>
+        <v>92264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>131989722</v>
       </c>
       <c r="B20" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>131989735</v>
       </c>
       <c r="B21" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,43 +2942,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131989700</v>
+        <v>131989725</v>
       </c>
       <c r="B22" t="n">
-        <v>58107</v>
+        <v>99098</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2987,10 +2986,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566496</v>
+        <v>566869</v>
       </c>
       <c r="R22" t="n">
-        <v>6679281</v>
+        <v>6679157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3032,7 +3031,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,10 +3058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989701</v>
+        <v>131989700</v>
       </c>
       <c r="B23" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,6 +3087,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3099,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566614</v>
+        <v>566496</v>
       </c>
       <c r="R23" t="n">
-        <v>6679286</v>
+        <v>6679281</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3144,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3171,38 +3175,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989742</v>
+        <v>131989701</v>
       </c>
       <c r="B24" t="n">
-        <v>8444</v>
+        <v>58109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3211,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566722</v>
+        <v>566614</v>
       </c>
       <c r="R24" t="n">
-        <v>6679268</v>
+        <v>6679286</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3246,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,7 +3260,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3283,42 +3287,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989725</v>
+        <v>131989742</v>
       </c>
       <c r="B25" t="n">
-        <v>99095</v>
+        <v>8444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566869</v>
+        <v>566722</v>
       </c>
       <c r="R25" t="n">
-        <v>6679157</v>
+        <v>6679268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,7 +3402,7 @@
         <v>131989686</v>
       </c>
       <c r="B26" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989691</v>
+        <v>131989687</v>
       </c>
       <c r="B27" t="n">
-        <v>91889</v>
+        <v>91855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566556</v>
+        <v>566505</v>
       </c>
       <c r="R27" t="n">
-        <v>6679090</v>
+        <v>6679080</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,54 +3613,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989717</v>
+        <v>131989691</v>
       </c>
       <c r="B28" t="n">
-        <v>99095</v>
+        <v>91892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566525</v>
+        <v>566556</v>
       </c>
       <c r="R28" t="n">
-        <v>6679095</v>
+        <v>6679090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3692,7 +3683,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3693,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,45 +3720,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989687</v>
+        <v>131989717</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>99098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566505</v>
+        <v>566525</v>
       </c>
       <c r="R29" t="n">
-        <v>6679080</v>
+        <v>6679095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,7 +3839,7 @@
         <v>131989713</v>
       </c>
       <c r="B30" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,32 +3952,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131989709</v>
+        <v>131989690</v>
       </c>
       <c r="B31" t="n">
-        <v>97960</v>
+        <v>91892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566652</v>
+        <v>566533</v>
       </c>
       <c r="R31" t="n">
-        <v>6679329</v>
+        <v>6679097</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,12 +4032,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>I gammal kolbotten</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,10 +4059,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131989710</v>
+        <v>131989709</v>
       </c>
       <c r="B32" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4099,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566626</v>
+        <v>566652</v>
       </c>
       <c r="R32" t="n">
-        <v>6679348</v>
+        <v>6679329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4134,7 +4129,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4144,7 +4139,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>I gammal kolbotten</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,32 +4171,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131989690</v>
+        <v>131989710</v>
       </c>
       <c r="B33" t="n">
-        <v>91889</v>
+        <v>97963</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566533</v>
+        <v>566626</v>
       </c>
       <c r="R33" t="n">
-        <v>6679097</v>
+        <v>6679348</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,38 +4278,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989744</v>
+        <v>131989714</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4318,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566439</v>
+        <v>566771</v>
       </c>
       <c r="R34" t="n">
-        <v>6679145</v>
+        <v>6679247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4353,7 +4362,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4363,7 +4372,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,10 +4399,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989714</v>
+        <v>131989729</v>
       </c>
       <c r="B35" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4420,7 +4429,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4428,21 +4437,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566771</v>
+        <v>566608</v>
       </c>
       <c r="R35" t="n">
-        <v>6679247</v>
+        <v>6679223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4484,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,42 +4515,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989729</v>
+        <v>131989744</v>
       </c>
       <c r="B36" t="n">
-        <v>99095</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566608</v>
+        <v>566439</v>
       </c>
       <c r="R36" t="n">
-        <v>6679223</v>
+        <v>6679145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,7 +4630,7 @@
         <v>131989732</v>
       </c>
       <c r="B37" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131989695</v>
+        <v>131989693</v>
       </c>
       <c r="B38" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566461</v>
+        <v>566484</v>
       </c>
       <c r="R38" t="n">
-        <v>6679189</v>
+        <v>6679089</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4853,7 +4853,7 @@
         <v>131989692</v>
       </c>
       <c r="B39" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131989693</v>
+        <v>131989695</v>
       </c>
       <c r="B40" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566484</v>
+        <v>566461</v>
       </c>
       <c r="R40" t="n">
-        <v>6679089</v>
+        <v>6679189</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5067,7 +5067,7 @@
         <v>131989721</v>
       </c>
       <c r="B41" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5180,42 +5180,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131989724</v>
+        <v>131989743</v>
       </c>
       <c r="B42" t="n">
-        <v>99095</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5224,10 +5220,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566527</v>
+        <v>566470</v>
       </c>
       <c r="R42" t="n">
-        <v>6679247</v>
+        <v>6679099</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5259,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5269,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5296,38 +5292,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131989743</v>
+        <v>131989724</v>
       </c>
       <c r="B43" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566470</v>
+        <v>566527</v>
       </c>
       <c r="R43" t="n">
-        <v>6679099</v>
+        <v>6679247</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -1804,42 +1804,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989712</v>
+        <v>131989703</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1848,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566598</v>
+        <v>566786</v>
       </c>
       <c r="R12" t="n">
-        <v>6679291</v>
+        <v>6679271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2036,38 +2032,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989703</v>
+        <v>131989712</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566786</v>
+        <v>566598</v>
       </c>
       <c r="R14" t="n">
-        <v>6679271</v>
+        <v>6679291</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2942,42 +2942,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131989725</v>
+        <v>131989700</v>
       </c>
       <c r="B22" t="n">
-        <v>99098</v>
+        <v>58109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2986,10 +2987,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566869</v>
+        <v>566496</v>
       </c>
       <c r="R22" t="n">
-        <v>6679157</v>
+        <v>6679281</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3021,7 +3022,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3031,7 +3032,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,7 +3059,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989700</v>
+        <v>131989701</v>
       </c>
       <c r="B23" t="n">
         <v>58109</v>
@@ -3087,11 +3088,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3103,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566496</v>
+        <v>566614</v>
       </c>
       <c r="R23" t="n">
-        <v>6679281</v>
+        <v>6679286</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3134,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3144,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,38 +3171,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989701</v>
+        <v>131989742</v>
       </c>
       <c r="B24" t="n">
-        <v>58109</v>
+        <v>8444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3215,10 +3211,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566614</v>
+        <v>566722</v>
       </c>
       <c r="R24" t="n">
-        <v>6679286</v>
+        <v>6679268</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,7 +3256,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,38 +3283,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989742</v>
+        <v>131989725</v>
       </c>
       <c r="B25" t="n">
-        <v>8444</v>
+        <v>99098</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566722</v>
+        <v>566869</v>
       </c>
       <c r="R25" t="n">
-        <v>6679268</v>
+        <v>6679157</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4278,47 +4278,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989714</v>
+        <v>131989744</v>
       </c>
       <c r="B34" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4327,10 +4318,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566771</v>
+        <v>566439</v>
       </c>
       <c r="R34" t="n">
-        <v>6679247</v>
+        <v>6679145</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4362,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4372,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,7 +4390,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989729</v>
+        <v>131989714</v>
       </c>
       <c r="B35" t="n">
         <v>99098</v>
@@ -4429,7 +4420,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4437,16 +4428,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566608</v>
+        <v>566771</v>
       </c>
       <c r="R35" t="n">
-        <v>6679223</v>
+        <v>6679247</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4474,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4484,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,38 +4511,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989744</v>
+        <v>131989729</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566439</v>
+        <v>566608</v>
       </c>
       <c r="R36" t="n">
-        <v>6679145</v>
+        <v>6679223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5180,38 +5180,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131989743</v>
+        <v>131989724</v>
       </c>
       <c r="B42" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5220,10 +5224,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566470</v>
+        <v>566527</v>
       </c>
       <c r="R42" t="n">
-        <v>6679099</v>
+        <v>6679247</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5255,7 +5259,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,7 +5269,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5292,42 +5296,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131989724</v>
+        <v>131989743</v>
       </c>
       <c r="B43" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566527</v>
+        <v>566470</v>
       </c>
       <c r="R43" t="n">
-        <v>6679247</v>
+        <v>6679099</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -2942,43 +2942,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131989700</v>
+        <v>131989725</v>
       </c>
       <c r="B22" t="n">
-        <v>58109</v>
+        <v>99098</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2987,10 +2986,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566496</v>
+        <v>566869</v>
       </c>
       <c r="R22" t="n">
-        <v>6679281</v>
+        <v>6679157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3032,7 +3031,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,7 +3058,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989701</v>
+        <v>131989700</v>
       </c>
       <c r="B23" t="n">
         <v>58109</v>
@@ -3088,6 +3087,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3099,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566614</v>
+        <v>566496</v>
       </c>
       <c r="R23" t="n">
-        <v>6679286</v>
+        <v>6679281</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3144,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3171,38 +3175,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989742</v>
+        <v>131989701</v>
       </c>
       <c r="B24" t="n">
-        <v>8444</v>
+        <v>58109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3211,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566722</v>
+        <v>566614</v>
       </c>
       <c r="R24" t="n">
-        <v>6679268</v>
+        <v>6679286</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3246,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,7 +3260,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3283,42 +3287,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989725</v>
+        <v>131989742</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>8444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566869</v>
+        <v>566722</v>
       </c>
       <c r="R25" t="n">
-        <v>6679157</v>
+        <v>6679268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3952,32 +3952,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131989690</v>
+        <v>131989709</v>
       </c>
       <c r="B31" t="n">
-        <v>91892</v>
+        <v>97963</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566533</v>
+        <v>566652</v>
       </c>
       <c r="R31" t="n">
-        <v>6679097</v>
+        <v>6679329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,7 +4032,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I gammal kolbotten</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4059,7 +4064,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131989709</v>
+        <v>131989710</v>
       </c>
       <c r="B32" t="n">
         <v>97963</v>
@@ -4094,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566652</v>
+        <v>566626</v>
       </c>
       <c r="R32" t="n">
-        <v>6679329</v>
+        <v>6679348</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,7 +4134,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4139,12 +4144,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>I gammal kolbotten</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,32 +4171,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131989710</v>
+        <v>131989690</v>
       </c>
       <c r="B33" t="n">
-        <v>97963</v>
+        <v>91892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566626</v>
+        <v>566533</v>
       </c>
       <c r="R33" t="n">
-        <v>6679348</v>
+        <v>6679097</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,38 +4278,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989744</v>
+        <v>131989714</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4318,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566439</v>
+        <v>566771</v>
       </c>
       <c r="R34" t="n">
-        <v>6679145</v>
+        <v>6679247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4353,7 +4362,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4363,7 +4372,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,7 +4399,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989714</v>
+        <v>131989729</v>
       </c>
       <c r="B35" t="n">
         <v>99098</v>
@@ -4420,7 +4429,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4428,21 +4437,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566771</v>
+        <v>566608</v>
       </c>
       <c r="R35" t="n">
-        <v>6679247</v>
+        <v>6679223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4484,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,42 +4515,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989729</v>
+        <v>131989744</v>
       </c>
       <c r="B36" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566608</v>
+        <v>566439</v>
       </c>
       <c r="R36" t="n">
-        <v>6679223</v>
+        <v>6679145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5180,42 +5180,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131989724</v>
+        <v>131989743</v>
       </c>
       <c r="B42" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5224,10 +5220,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566527</v>
+        <v>566470</v>
       </c>
       <c r="R42" t="n">
-        <v>6679247</v>
+        <v>6679099</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5259,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5269,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5296,38 +5292,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131989743</v>
+        <v>131989724</v>
       </c>
       <c r="B43" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566470</v>
+        <v>566527</v>
       </c>
       <c r="R43" t="n">
-        <v>6679099</v>
+        <v>6679247</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131989685</v>
+        <v>131989734</v>
       </c>
       <c r="B2" t="n">
-        <v>91855</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566683</v>
+        <v>566886</v>
       </c>
       <c r="R2" t="n">
-        <v>6679245</v>
+        <v>6679158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,54 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131989734</v>
+        <v>131989685</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>91855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566886</v>
+        <v>566683</v>
       </c>
       <c r="R3" t="n">
-        <v>6679158</v>
+        <v>6679245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,45 +898,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131989697</v>
+        <v>131989726</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566627</v>
+        <v>566577</v>
       </c>
       <c r="R4" t="n">
-        <v>6679348</v>
+        <v>6679273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,50 +1014,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131989698</v>
+        <v>131989697</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566601</v>
+        <v>566627</v>
       </c>
       <c r="R5" t="n">
-        <v>6679232</v>
+        <v>6679348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,42 +1121,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131989726</v>
+        <v>131989698</v>
       </c>
       <c r="B6" t="n">
-        <v>99098</v>
+        <v>4775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566577</v>
+        <v>566601</v>
       </c>
       <c r="R6" t="n">
-        <v>6679273</v>
+        <v>6679232</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,45 +1233,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131989688</v>
+        <v>131989716</v>
       </c>
       <c r="B7" t="n">
-        <v>91855</v>
+        <v>99098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566662</v>
+        <v>566574</v>
       </c>
       <c r="R7" t="n">
-        <v>6679349</v>
+        <v>6679277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131989716</v>
+        <v>131989730</v>
       </c>
       <c r="B8" t="n">
         <v>99098</v>
@@ -1370,7 +1379,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1384,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566574</v>
+        <v>566655</v>
       </c>
       <c r="R8" t="n">
-        <v>6679277</v>
+        <v>6679324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,54 +1465,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131989730</v>
+        <v>131989688</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>91855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566655</v>
+        <v>566662</v>
       </c>
       <c r="R9" t="n">
-        <v>6679324</v>
+        <v>6679349</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989718</v>
+        <v>131989712</v>
       </c>
       <c r="B13" t="n">
         <v>99098</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566526</v>
+        <v>566598</v>
       </c>
       <c r="R13" t="n">
-        <v>6679221</v>
+        <v>6679291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989712</v>
+        <v>131989718</v>
       </c>
       <c r="B14" t="n">
         <v>99098</v>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566598</v>
+        <v>566526</v>
       </c>
       <c r="R14" t="n">
-        <v>6679291</v>
+        <v>6679221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,45 +2148,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131989696</v>
+        <v>131989715</v>
       </c>
       <c r="B15" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566485</v>
+        <v>566602</v>
       </c>
       <c r="R15" t="n">
-        <v>6679257</v>
+        <v>6679219</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2228,7 +2237,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2264,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131989715</v>
+        <v>131989720</v>
       </c>
       <c r="B16" t="n">
         <v>99098</v>
@@ -2285,7 +2294,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2299,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566602</v>
+        <v>566600</v>
       </c>
       <c r="R16" t="n">
-        <v>6679219</v>
+        <v>6679228</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,7 +2380,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131989720</v>
+        <v>131989731</v>
       </c>
       <c r="B17" t="n">
         <v>99098</v>
@@ -2401,7 +2410,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2415,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566600</v>
+        <v>566563</v>
       </c>
       <c r="R17" t="n">
-        <v>6679228</v>
+        <v>6679314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2469,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,54 +2496,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131989731</v>
+        <v>131989696</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566563</v>
+        <v>566485</v>
       </c>
       <c r="R18" t="n">
-        <v>6679314</v>
+        <v>6679257</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131989689</v>
+        <v>131989722</v>
       </c>
       <c r="B19" t="n">
-        <v>92264</v>
+        <v>99098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,34 +2614,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566483</v>
+        <v>566570</v>
       </c>
       <c r="R19" t="n">
-        <v>6679261</v>
+        <v>6679277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2682,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,7 +2692,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,7 +2719,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131989722</v>
+        <v>131989735</v>
       </c>
       <c r="B20" t="n">
         <v>99098</v>
@@ -2740,7 +2749,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2754,10 +2763,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566570</v>
+        <v>566580</v>
       </c>
       <c r="R20" t="n">
-        <v>6679277</v>
+        <v>6679241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,7 +2798,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2799,7 +2808,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,10 +2835,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131989735</v>
+        <v>131989689</v>
       </c>
       <c r="B21" t="n">
-        <v>99098</v>
+        <v>92264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,43 +2846,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566580</v>
+        <v>566483</v>
       </c>
       <c r="R21" t="n">
-        <v>6679241</v>
+        <v>6679261</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,42 +2942,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131989725</v>
+        <v>131989742</v>
       </c>
       <c r="B22" t="n">
-        <v>99098</v>
+        <v>8444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2986,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566869</v>
+        <v>566722</v>
       </c>
       <c r="R22" t="n">
-        <v>6679157</v>
+        <v>6679268</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3021,7 +3017,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3031,7 +3027,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,43 +3054,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989700</v>
+        <v>131989725</v>
       </c>
       <c r="B23" t="n">
-        <v>58109</v>
+        <v>99098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3103,10 +3098,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566496</v>
+        <v>566869</v>
       </c>
       <c r="R23" t="n">
-        <v>6679281</v>
+        <v>6679157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3133,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3143,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,7 +3170,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989701</v>
+        <v>131989700</v>
       </c>
       <c r="B24" t="n">
         <v>58109</v>
@@ -3204,6 +3199,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566614</v>
+        <v>566496</v>
       </c>
       <c r="R24" t="n">
-        <v>6679286</v>
+        <v>6679281</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,38 +3287,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989742</v>
+        <v>131989701</v>
       </c>
       <c r="B25" t="n">
-        <v>8444</v>
+        <v>58109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566722</v>
+        <v>566614</v>
       </c>
       <c r="R25" t="n">
-        <v>6679268</v>
+        <v>6679286</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3506,45 +3506,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989687</v>
+        <v>131989717</v>
       </c>
       <c r="B27" t="n">
-        <v>91855</v>
+        <v>99098</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566505</v>
+        <v>566525</v>
       </c>
       <c r="R27" t="n">
-        <v>6679080</v>
+        <v>6679095</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3720,54 +3729,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989717</v>
+        <v>131989687</v>
       </c>
       <c r="B29" t="n">
-        <v>99098</v>
+        <v>91855</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566525</v>
+        <v>566505</v>
       </c>
       <c r="R29" t="n">
-        <v>6679095</v>
+        <v>6679080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3952,32 +3952,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131989709</v>
+        <v>131989690</v>
       </c>
       <c r="B31" t="n">
-        <v>97963</v>
+        <v>91892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566652</v>
+        <v>566533</v>
       </c>
       <c r="R31" t="n">
-        <v>6679329</v>
+        <v>6679097</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,12 +4032,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>I gammal kolbotten</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131989710</v>
+        <v>131989709</v>
       </c>
       <c r="B32" t="n">
         <v>97963</v>
@@ -4099,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566626</v>
+        <v>566652</v>
       </c>
       <c r="R32" t="n">
-        <v>6679348</v>
+        <v>6679329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4134,7 +4129,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4144,7 +4139,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>I gammal kolbotten</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,32 +4171,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131989690</v>
+        <v>131989710</v>
       </c>
       <c r="B33" t="n">
-        <v>91892</v>
+        <v>97963</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566533</v>
+        <v>566626</v>
       </c>
       <c r="R33" t="n">
-        <v>6679097</v>
+        <v>6679348</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,47 +4278,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989714</v>
+        <v>131989744</v>
       </c>
       <c r="B34" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4327,10 +4318,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566771</v>
+        <v>566439</v>
       </c>
       <c r="R34" t="n">
-        <v>6679247</v>
+        <v>6679145</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4362,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4372,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,7 +4390,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989729</v>
+        <v>131989714</v>
       </c>
       <c r="B35" t="n">
         <v>99098</v>
@@ -4429,7 +4420,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4437,16 +4428,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566608</v>
+        <v>566771</v>
       </c>
       <c r="R35" t="n">
-        <v>6679223</v>
+        <v>6679247</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4474,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4484,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,38 +4511,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989744</v>
+        <v>131989729</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566439</v>
+        <v>566608</v>
       </c>
       <c r="R36" t="n">
-        <v>6679145</v>
+        <v>6679223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4743,7 +4743,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131989693</v>
+        <v>131989695</v>
       </c>
       <c r="B38" t="n">
         <v>91892</v>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566484</v>
+        <v>566461</v>
       </c>
       <c r="R38" t="n">
-        <v>6679089</v>
+        <v>6679189</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4957,7 +4957,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131989695</v>
+        <v>131989693</v>
       </c>
       <c r="B40" t="n">
         <v>91892</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566461</v>
+        <v>566484</v>
       </c>
       <c r="R40" t="n">
-        <v>6679189</v>
+        <v>6679089</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -1804,38 +1804,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989703</v>
+        <v>131989712</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1844,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566786</v>
+        <v>566598</v>
       </c>
       <c r="R12" t="n">
-        <v>6679271</v>
+        <v>6679291</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989712</v>
+        <v>131989718</v>
       </c>
       <c r="B13" t="n">
         <v>99098</v>
@@ -1946,7 +1950,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1960,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566598</v>
+        <v>566526</v>
       </c>
       <c r="R13" t="n">
-        <v>6679291</v>
+        <v>6679221</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1999,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2009,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,42 +2036,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989718</v>
+        <v>131989703</v>
       </c>
       <c r="B14" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566526</v>
+        <v>566786</v>
       </c>
       <c r="R14" t="n">
-        <v>6679221</v>
+        <v>6679271</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -1233,54 +1233,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131989716</v>
+        <v>131989688</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>91855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566574</v>
+        <v>566662</v>
       </c>
       <c r="R7" t="n">
-        <v>6679277</v>
+        <v>6679349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131989730</v>
+        <v>131989716</v>
       </c>
       <c r="B8" t="n">
         <v>99098</v>
@@ -1379,7 +1370,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1393,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566655</v>
+        <v>566574</v>
       </c>
       <c r="R8" t="n">
-        <v>6679324</v>
+        <v>6679277</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,45 +1456,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131989688</v>
+        <v>131989730</v>
       </c>
       <c r="B9" t="n">
-        <v>91855</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566662</v>
+        <v>566655</v>
       </c>
       <c r="R9" t="n">
-        <v>6679349</v>
+        <v>6679324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1804,42 +1804,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989712</v>
+        <v>131989703</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1848,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566598</v>
+        <v>566786</v>
       </c>
       <c r="R12" t="n">
-        <v>6679291</v>
+        <v>6679271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989718</v>
+        <v>131989712</v>
       </c>
       <c r="B13" t="n">
         <v>99098</v>
@@ -1950,7 +1946,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1964,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566526</v>
+        <v>566598</v>
       </c>
       <c r="R13" t="n">
-        <v>6679221</v>
+        <v>6679291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,38 +2032,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989703</v>
+        <v>131989718</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566786</v>
+        <v>566526</v>
       </c>
       <c r="R14" t="n">
-        <v>6679271</v>
+        <v>6679221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3506,54 +3506,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989717</v>
+        <v>131989691</v>
       </c>
       <c r="B27" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566525</v>
+        <v>566556</v>
       </c>
       <c r="R27" t="n">
-        <v>6679095</v>
+        <v>6679090</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3585,7 +3576,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3586,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3622,32 +3613,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989691</v>
+        <v>131989687</v>
       </c>
       <c r="B28" t="n">
-        <v>91892</v>
+        <v>91855</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3657,10 +3648,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566556</v>
+        <v>566505</v>
       </c>
       <c r="R28" t="n">
-        <v>6679090</v>
+        <v>6679080</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3692,7 +3683,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3693,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,45 +3720,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989687</v>
+        <v>131989717</v>
       </c>
       <c r="B29" t="n">
-        <v>91855</v>
+        <v>99098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566505</v>
+        <v>566525</v>
       </c>
       <c r="R29" t="n">
-        <v>6679080</v>
+        <v>6679095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131989734</v>
+        <v>131989685</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>91861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566886</v>
+        <v>566683</v>
       </c>
       <c r="R2" t="n">
-        <v>6679158</v>
+        <v>6679245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131989685</v>
+        <v>131989734</v>
       </c>
       <c r="B3" t="n">
-        <v>91855</v>
+        <v>99106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566683</v>
+        <v>566886</v>
       </c>
       <c r="R3" t="n">
-        <v>6679245</v>
+        <v>6679158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,54 +898,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131989726</v>
+        <v>131989697</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>91898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566577</v>
+        <v>566627</v>
       </c>
       <c r="R4" t="n">
-        <v>6679273</v>
+        <v>6679348</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,45 +1005,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131989697</v>
+        <v>131989698</v>
       </c>
       <c r="B5" t="n">
-        <v>91892</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566627</v>
+        <v>566601</v>
       </c>
       <c r="R5" t="n">
-        <v>6679348</v>
+        <v>6679232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,38 +1117,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131989698</v>
+        <v>131989726</v>
       </c>
       <c r="B6" t="n">
-        <v>4775</v>
+        <v>99106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566601</v>
+        <v>566577</v>
       </c>
       <c r="R6" t="n">
-        <v>6679232</v>
+        <v>6679273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1236,7 @@
         <v>131989688</v>
       </c>
       <c r="B7" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>131989716</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131989730</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>131989728</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>131989719</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,42 +1804,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989712</v>
+        <v>131989703</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>57946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1848,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566598</v>
+        <v>566786</v>
       </c>
       <c r="R12" t="n">
-        <v>6679291</v>
+        <v>6679271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989718</v>
+        <v>131989712</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1946,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1964,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566526</v>
+        <v>566598</v>
       </c>
       <c r="R13" t="n">
-        <v>6679221</v>
+        <v>6679291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,38 +2032,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989703</v>
+        <v>131989718</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>99106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566786</v>
+        <v>566526</v>
       </c>
       <c r="R14" t="n">
-        <v>6679271</v>
+        <v>6679221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,7 +2151,7 @@
         <v>131989715</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>131989720</v>
       </c>
       <c r="B16" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>131989731</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>131989696</v>
       </c>
       <c r="B18" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>131989722</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>131989735</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>131989689</v>
       </c>
       <c r="B21" t="n">
-        <v>92264</v>
+        <v>92270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,38 +2942,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131989742</v>
+        <v>131989700</v>
       </c>
       <c r="B22" t="n">
-        <v>8444</v>
+        <v>58110</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566722</v>
+        <v>566496</v>
       </c>
       <c r="R22" t="n">
-        <v>6679268</v>
+        <v>6679281</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3022,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3027,7 +3032,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,42 +3059,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989725</v>
+        <v>131989701</v>
       </c>
       <c r="B23" t="n">
-        <v>99098</v>
+        <v>58110</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3098,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566869</v>
+        <v>566614</v>
       </c>
       <c r="R23" t="n">
-        <v>6679157</v>
+        <v>6679286</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3133,7 +3134,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3143,7 +3144,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,43 +3171,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989700</v>
+        <v>131989725</v>
       </c>
       <c r="B24" t="n">
-        <v>58109</v>
+        <v>99106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566496</v>
+        <v>566869</v>
       </c>
       <c r="R24" t="n">
-        <v>6679281</v>
+        <v>6679157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,38 +3287,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989701</v>
+        <v>131989742</v>
       </c>
       <c r="B25" t="n">
-        <v>58109</v>
+        <v>8444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566614</v>
+        <v>566722</v>
       </c>
       <c r="R25" t="n">
-        <v>6679286</v>
+        <v>6679268</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,7 +3402,7 @@
         <v>131989686</v>
       </c>
       <c r="B26" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989691</v>
+        <v>131989687</v>
       </c>
       <c r="B27" t="n">
-        <v>91892</v>
+        <v>91861</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566556</v>
+        <v>566505</v>
       </c>
       <c r="R27" t="n">
-        <v>6679090</v>
+        <v>6679080</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,32 +3613,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989687</v>
+        <v>131989691</v>
       </c>
       <c r="B28" t="n">
-        <v>91855</v>
+        <v>91898</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566505</v>
+        <v>566556</v>
       </c>
       <c r="R28" t="n">
-        <v>6679080</v>
+        <v>6679090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,7 +3723,7 @@
         <v>131989717</v>
       </c>
       <c r="B29" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>131989713</v>
       </c>
       <c r="B30" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,32 +3952,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131989690</v>
+        <v>131989709</v>
       </c>
       <c r="B31" t="n">
-        <v>91892</v>
+        <v>97971</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566533</v>
+        <v>566652</v>
       </c>
       <c r="R31" t="n">
-        <v>6679097</v>
+        <v>6679329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,7 +4032,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I gammal kolbotten</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4059,10 +4064,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131989709</v>
+        <v>131989710</v>
       </c>
       <c r="B32" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566652</v>
+        <v>566626</v>
       </c>
       <c r="R32" t="n">
-        <v>6679329</v>
+        <v>6679348</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,7 +4134,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4139,12 +4144,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>I gammal kolbotten</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,32 +4171,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131989710</v>
+        <v>131989690</v>
       </c>
       <c r="B33" t="n">
-        <v>97963</v>
+        <v>91898</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566626</v>
+        <v>566533</v>
       </c>
       <c r="R33" t="n">
-        <v>6679348</v>
+        <v>6679097</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,38 +4278,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989744</v>
+        <v>131989714</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>99106</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4318,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566439</v>
+        <v>566771</v>
       </c>
       <c r="R34" t="n">
-        <v>6679145</v>
+        <v>6679247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4353,7 +4362,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4363,7 +4372,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,10 +4399,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989714</v>
+        <v>131989729</v>
       </c>
       <c r="B35" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4420,7 +4429,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4428,21 +4437,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566771</v>
+        <v>566608</v>
       </c>
       <c r="R35" t="n">
-        <v>6679247</v>
+        <v>6679223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4484,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,42 +4515,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989729</v>
+        <v>131989744</v>
       </c>
       <c r="B36" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566608</v>
+        <v>566439</v>
       </c>
       <c r="R36" t="n">
-        <v>6679223</v>
+        <v>6679145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,7 +4630,7 @@
         <v>131989732</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>131989695</v>
       </c>
       <c r="B38" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>131989692</v>
       </c>
       <c r="B39" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>131989693</v>
       </c>
       <c r="B40" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>131989721</v>
       </c>
       <c r="B41" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5180,38 +5180,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131989743</v>
+        <v>131989724</v>
       </c>
       <c r="B42" t="n">
-        <v>5179</v>
+        <v>99106</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5220,10 +5224,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566470</v>
+        <v>566527</v>
       </c>
       <c r="R42" t="n">
-        <v>6679099</v>
+        <v>6679247</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5255,7 +5259,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,7 +5269,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5292,42 +5296,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131989724</v>
+        <v>131989743</v>
       </c>
       <c r="B43" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566527</v>
+        <v>566470</v>
       </c>
       <c r="R43" t="n">
-        <v>6679247</v>
+        <v>6679099</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131989685</v>
+        <v>131989734</v>
       </c>
       <c r="B2" t="n">
-        <v>91861</v>
+        <v>99106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566683</v>
+        <v>566886</v>
       </c>
       <c r="R2" t="n">
-        <v>6679245</v>
+        <v>6679158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,54 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131989734</v>
+        <v>131989685</v>
       </c>
       <c r="B3" t="n">
-        <v>99106</v>
+        <v>91861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566886</v>
+        <v>566683</v>
       </c>
       <c r="R3" t="n">
-        <v>6679158</v>
+        <v>6679245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1233,45 +1233,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131989688</v>
+        <v>131989716</v>
       </c>
       <c r="B7" t="n">
-        <v>91861</v>
+        <v>99106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566662</v>
+        <v>566574</v>
       </c>
       <c r="R7" t="n">
-        <v>6679349</v>
+        <v>6679277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131989716</v>
+        <v>131989730</v>
       </c>
       <c r="B8" t="n">
         <v>99106</v>
@@ -1370,7 +1379,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1384,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566574</v>
+        <v>566655</v>
       </c>
       <c r="R8" t="n">
-        <v>6679277</v>
+        <v>6679324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,54 +1465,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131989730</v>
+        <v>131989688</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>91861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566655</v>
+        <v>566662</v>
       </c>
       <c r="R9" t="n">
-        <v>6679324</v>
+        <v>6679349</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2603,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131989722</v>
+        <v>131989689</v>
       </c>
       <c r="B19" t="n">
-        <v>99106</v>
+        <v>92270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,43 +2614,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566570</v>
+        <v>566483</v>
       </c>
       <c r="R19" t="n">
-        <v>6679277</v>
+        <v>6679261</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,7 +2673,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,7 +2683,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,7 +2710,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131989735</v>
+        <v>131989722</v>
       </c>
       <c r="B20" t="n">
         <v>99106</v>
@@ -2749,7 +2740,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2763,10 +2754,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566580</v>
+        <v>566570</v>
       </c>
       <c r="R20" t="n">
-        <v>6679241</v>
+        <v>6679277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2798,7 +2789,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2808,7 +2799,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131989689</v>
+        <v>131989735</v>
       </c>
       <c r="B21" t="n">
-        <v>92270</v>
+        <v>99106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,34 +2837,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566483</v>
+        <v>566580</v>
       </c>
       <c r="R21" t="n">
-        <v>6679261</v>
+        <v>6679241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3952,32 +3952,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131989709</v>
+        <v>131989690</v>
       </c>
       <c r="B31" t="n">
-        <v>97971</v>
+        <v>91898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566652</v>
+        <v>566533</v>
       </c>
       <c r="R31" t="n">
-        <v>6679329</v>
+        <v>6679097</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,12 +4032,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>I gammal kolbotten</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131989710</v>
+        <v>131989709</v>
       </c>
       <c r="B32" t="n">
         <v>97971</v>
@@ -4099,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566626</v>
+        <v>566652</v>
       </c>
       <c r="R32" t="n">
-        <v>6679348</v>
+        <v>6679329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4134,7 +4129,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4144,7 +4139,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>I gammal kolbotten</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,32 +4171,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131989690</v>
+        <v>131989710</v>
       </c>
       <c r="B33" t="n">
-        <v>91898</v>
+        <v>97971</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566533</v>
+        <v>566626</v>
       </c>
       <c r="R33" t="n">
-        <v>6679097</v>
+        <v>6679348</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,47 +4278,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989714</v>
+        <v>131989744</v>
       </c>
       <c r="B34" t="n">
-        <v>99106</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4327,10 +4318,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566771</v>
+        <v>566439</v>
       </c>
       <c r="R34" t="n">
-        <v>6679247</v>
+        <v>6679145</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4362,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4372,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,7 +4390,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989729</v>
+        <v>131989714</v>
       </c>
       <c r="B35" t="n">
         <v>99106</v>
@@ -4429,7 +4420,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4437,16 +4428,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566608</v>
+        <v>566771</v>
       </c>
       <c r="R35" t="n">
-        <v>6679223</v>
+        <v>6679247</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4474,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4484,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,38 +4511,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989744</v>
+        <v>131989729</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>99106</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566439</v>
+        <v>566608</v>
       </c>
       <c r="R36" t="n">
-        <v>6679145</v>
+        <v>6679223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4743,45 +4743,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131989695</v>
+        <v>131989721</v>
       </c>
       <c r="B38" t="n">
-        <v>91898</v>
+        <v>99106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566461</v>
+        <v>566585</v>
       </c>
       <c r="R38" t="n">
-        <v>6679189</v>
+        <v>6679241</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4850,7 +4859,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131989692</v>
+        <v>131989695</v>
       </c>
       <c r="B39" t="n">
         <v>91898</v>
@@ -4885,10 +4894,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566516</v>
+        <v>566461</v>
       </c>
       <c r="R39" t="n">
-        <v>6679071</v>
+        <v>6679189</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4920,7 +4929,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4930,7 +4939,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4957,7 +4966,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131989693</v>
+        <v>131989692</v>
       </c>
       <c r="B40" t="n">
         <v>91898</v>
@@ -4992,10 +5001,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566484</v>
+        <v>566516</v>
       </c>
       <c r="R40" t="n">
-        <v>6679089</v>
+        <v>6679071</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5027,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5037,7 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5064,54 +5073,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131989721</v>
+        <v>131989693</v>
       </c>
       <c r="B41" t="n">
-        <v>99106</v>
+        <v>91898</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566585</v>
+        <v>566484</v>
       </c>
       <c r="R41" t="n">
-        <v>6679241</v>
+        <v>6679089</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131989734</v>
+        <v>131989685</v>
       </c>
       <c r="B2" t="n">
-        <v>99106</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566886</v>
+        <v>566683</v>
       </c>
       <c r="R2" t="n">
-        <v>6679158</v>
+        <v>6679245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131989685</v>
+        <v>131989734</v>
       </c>
       <c r="B3" t="n">
-        <v>91861</v>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566683</v>
+        <v>566886</v>
       </c>
       <c r="R3" t="n">
-        <v>6679245</v>
+        <v>6679158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,45 +898,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131989697</v>
+        <v>131989698</v>
       </c>
       <c r="B4" t="n">
-        <v>91898</v>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566627</v>
+        <v>566601</v>
       </c>
       <c r="R4" t="n">
-        <v>6679348</v>
+        <v>6679232</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,50 +1010,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131989698</v>
+        <v>131989697</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>91908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566601</v>
+        <v>566627</v>
       </c>
       <c r="R5" t="n">
-        <v>6679232</v>
+        <v>6679348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1120,7 @@
         <v>131989726</v>
       </c>
       <c r="B6" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>131989716</v>
       </c>
       <c r="B7" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,54 +1349,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131989730</v>
+        <v>131989688</v>
       </c>
       <c r="B8" t="n">
-        <v>99106</v>
+        <v>91871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566655</v>
+        <v>566662</v>
       </c>
       <c r="R8" t="n">
-        <v>6679324</v>
+        <v>6679349</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,45 +1456,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131989688</v>
+        <v>131989730</v>
       </c>
       <c r="B9" t="n">
-        <v>91861</v>
+        <v>99116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566662</v>
+        <v>566655</v>
       </c>
       <c r="R9" t="n">
-        <v>6679349</v>
+        <v>6679324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>131989728</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>131989719</v>
       </c>
       <c r="B11" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>131989703</v>
       </c>
       <c r="B12" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>131989712</v>
       </c>
       <c r="B13" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>131989718</v>
       </c>
       <c r="B14" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>131989715</v>
       </c>
       <c r="B15" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>131989720</v>
       </c>
       <c r="B16" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>131989731</v>
       </c>
       <c r="B17" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>131989696</v>
       </c>
       <c r="B18" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>131989689</v>
       </c>
       <c r="B19" t="n">
-        <v>92270</v>
+        <v>92280</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>131989722</v>
       </c>
       <c r="B20" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>131989735</v>
       </c>
       <c r="B21" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,43 +2942,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131989700</v>
+        <v>131989725</v>
       </c>
       <c r="B22" t="n">
-        <v>58110</v>
+        <v>99116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2987,10 +2986,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566496</v>
+        <v>566869</v>
       </c>
       <c r="R22" t="n">
-        <v>6679281</v>
+        <v>6679157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3032,7 +3031,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,10 +3058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989701</v>
+        <v>131989700</v>
       </c>
       <c r="B23" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,6 +3087,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3099,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566614</v>
+        <v>566496</v>
       </c>
       <c r="R23" t="n">
-        <v>6679286</v>
+        <v>6679281</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3144,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3171,42 +3175,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989725</v>
+        <v>131989701</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566869</v>
+        <v>566614</v>
       </c>
       <c r="R24" t="n">
-        <v>6679157</v>
+        <v>6679286</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3402,7 +3402,7 @@
         <v>131989686</v>
       </c>
       <c r="B26" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989687</v>
+        <v>131989691</v>
       </c>
       <c r="B27" t="n">
-        <v>91861</v>
+        <v>91908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566505</v>
+        <v>566556</v>
       </c>
       <c r="R27" t="n">
-        <v>6679080</v>
+        <v>6679090</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,45 +3613,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989691</v>
+        <v>131989717</v>
       </c>
       <c r="B28" t="n">
-        <v>91898</v>
+        <v>99116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566556</v>
+        <v>566525</v>
       </c>
       <c r="R28" t="n">
-        <v>6679090</v>
+        <v>6679095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3683,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3693,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3720,54 +3729,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989717</v>
+        <v>131989687</v>
       </c>
       <c r="B29" t="n">
-        <v>99106</v>
+        <v>91871</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566525</v>
+        <v>566505</v>
       </c>
       <c r="R29" t="n">
-        <v>6679095</v>
+        <v>6679080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,7 +3839,7 @@
         <v>131989713</v>
       </c>
       <c r="B30" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,32 +3952,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131989690</v>
+        <v>131989709</v>
       </c>
       <c r="B31" t="n">
-        <v>91898</v>
+        <v>97981</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566533</v>
+        <v>566652</v>
       </c>
       <c r="R31" t="n">
-        <v>6679097</v>
+        <v>6679329</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,7 +4032,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I gammal kolbotten</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4059,10 +4064,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131989709</v>
+        <v>131989710</v>
       </c>
       <c r="B32" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566652</v>
+        <v>566626</v>
       </c>
       <c r="R32" t="n">
-        <v>6679329</v>
+        <v>6679348</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,7 +4134,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4139,12 +4144,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>I gammal kolbotten</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,32 +4171,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131989710</v>
+        <v>131989690</v>
       </c>
       <c r="B33" t="n">
-        <v>97971</v>
+        <v>91908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566626</v>
+        <v>566533</v>
       </c>
       <c r="R33" t="n">
-        <v>6679348</v>
+        <v>6679097</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,38 +4278,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989744</v>
+        <v>131989714</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>99116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4318,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566439</v>
+        <v>566771</v>
       </c>
       <c r="R34" t="n">
-        <v>6679145</v>
+        <v>6679247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4353,7 +4362,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4363,7 +4372,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,10 +4399,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989714</v>
+        <v>131989729</v>
       </c>
       <c r="B35" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4420,7 +4429,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4428,21 +4437,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566771</v>
+        <v>566608</v>
       </c>
       <c r="R35" t="n">
-        <v>6679247</v>
+        <v>6679223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4484,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,42 +4515,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989729</v>
+        <v>131989744</v>
       </c>
       <c r="B36" t="n">
-        <v>99106</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566608</v>
+        <v>566439</v>
       </c>
       <c r="R36" t="n">
-        <v>6679223</v>
+        <v>6679145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,7 +4630,7 @@
         <v>131989732</v>
       </c>
       <c r="B37" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,54 +4743,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131989721</v>
+        <v>131989693</v>
       </c>
       <c r="B38" t="n">
-        <v>99106</v>
+        <v>91908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566585</v>
+        <v>566484</v>
       </c>
       <c r="R38" t="n">
-        <v>6679241</v>
+        <v>6679089</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4822,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4823,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4850,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131989695</v>
+        <v>131989692</v>
       </c>
       <c r="B39" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,10 +4885,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566461</v>
+        <v>566516</v>
       </c>
       <c r="R39" t="n">
-        <v>6679189</v>
+        <v>6679071</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4929,7 +4920,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4939,7 +4930,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4966,10 +4957,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131989692</v>
+        <v>131989695</v>
       </c>
       <c r="B40" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5001,10 +4992,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566516</v>
+        <v>566461</v>
       </c>
       <c r="R40" t="n">
-        <v>6679071</v>
+        <v>6679189</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5036,7 +5027,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5037,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5073,45 +5064,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131989693</v>
+        <v>131989721</v>
       </c>
       <c r="B41" t="n">
-        <v>91898</v>
+        <v>99116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566484</v>
+        <v>566585</v>
       </c>
       <c r="R41" t="n">
-        <v>6679089</v>
+        <v>6679241</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5180,42 +5180,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131989724</v>
+        <v>131989743</v>
       </c>
       <c r="B42" t="n">
-        <v>99106</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5224,10 +5220,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566527</v>
+        <v>566470</v>
       </c>
       <c r="R42" t="n">
-        <v>6679247</v>
+        <v>6679099</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5259,7 +5255,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5269,7 +5265,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5296,38 +5292,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131989743</v>
+        <v>131989724</v>
       </c>
       <c r="B43" t="n">
-        <v>5179</v>
+        <v>99116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566470</v>
+        <v>566527</v>
       </c>
       <c r="R43" t="n">
-        <v>6679099</v>
+        <v>6679247</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131989685</v>
+        <v>131989734</v>
       </c>
       <c r="B2" t="n">
-        <v>91871</v>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566683</v>
+        <v>566886</v>
       </c>
       <c r="R2" t="n">
-        <v>6679245</v>
+        <v>6679158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,54 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131989734</v>
+        <v>131989685</v>
       </c>
       <c r="B3" t="n">
-        <v>99116</v>
+        <v>91871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566886</v>
+        <v>566683</v>
       </c>
       <c r="R3" t="n">
-        <v>6679158</v>
+        <v>6679245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2710,7 +2710,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131989722</v>
+        <v>131989735</v>
       </c>
       <c r="B20" t="n">
         <v>99116</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566570</v>
+        <v>566580</v>
       </c>
       <c r="R20" t="n">
-        <v>6679277</v>
+        <v>6679241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,7 +2826,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131989735</v>
+        <v>131989722</v>
       </c>
       <c r="B21" t="n">
         <v>99116</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566580</v>
+        <v>566570</v>
       </c>
       <c r="R21" t="n">
-        <v>6679241</v>
+        <v>6679277</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,42 +2942,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131989725</v>
+        <v>131989742</v>
       </c>
       <c r="B22" t="n">
-        <v>99116</v>
+        <v>8444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2986,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566869</v>
+        <v>566722</v>
       </c>
       <c r="R22" t="n">
-        <v>6679157</v>
+        <v>6679268</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3021,7 +3017,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3031,7 +3027,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3287,38 +3283,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989742</v>
+        <v>131989725</v>
       </c>
       <c r="B25" t="n">
-        <v>8444</v>
+        <v>99116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566722</v>
+        <v>566869</v>
       </c>
       <c r="R25" t="n">
-        <v>6679268</v>
+        <v>6679157</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3506,45 +3506,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989691</v>
+        <v>131989717</v>
       </c>
       <c r="B27" t="n">
-        <v>91908</v>
+        <v>99116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566556</v>
+        <v>566525</v>
       </c>
       <c r="R27" t="n">
-        <v>6679090</v>
+        <v>6679095</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,54 +3622,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989717</v>
+        <v>131989687</v>
       </c>
       <c r="B28" t="n">
-        <v>99116</v>
+        <v>91871</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566525</v>
+        <v>566505</v>
       </c>
       <c r="R28" t="n">
-        <v>6679095</v>
+        <v>6679080</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,32 +3729,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989687</v>
+        <v>131989691</v>
       </c>
       <c r="B29" t="n">
-        <v>91871</v>
+        <v>91908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566505</v>
+        <v>566556</v>
       </c>
       <c r="R29" t="n">
-        <v>6679080</v>
+        <v>6679090</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4278,47 +4278,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989714</v>
+        <v>131989744</v>
       </c>
       <c r="B34" t="n">
-        <v>99116</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4327,10 +4318,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566771</v>
+        <v>566439</v>
       </c>
       <c r="R34" t="n">
-        <v>6679247</v>
+        <v>6679145</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4362,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4372,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,7 +4390,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989729</v>
+        <v>131989714</v>
       </c>
       <c r="B35" t="n">
         <v>99116</v>
@@ -4429,7 +4420,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4437,16 +4428,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566608</v>
+        <v>566771</v>
       </c>
       <c r="R35" t="n">
-        <v>6679223</v>
+        <v>6679247</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4474,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4484,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,38 +4511,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989744</v>
+        <v>131989729</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>99116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566439</v>
+        <v>566608</v>
       </c>
       <c r="R36" t="n">
-        <v>6679145</v>
+        <v>6679223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4743,45 +4743,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131989693</v>
+        <v>131989721</v>
       </c>
       <c r="B38" t="n">
-        <v>91908</v>
+        <v>99116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566484</v>
+        <v>566585</v>
       </c>
       <c r="R38" t="n">
-        <v>6679089</v>
+        <v>6679241</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4850,7 +4859,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131989692</v>
+        <v>131989693</v>
       </c>
       <c r="B39" t="n">
         <v>91908</v>
@@ -4885,10 +4894,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566516</v>
+        <v>566484</v>
       </c>
       <c r="R39" t="n">
-        <v>6679071</v>
+        <v>6679089</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4920,7 +4929,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4930,7 +4939,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4957,7 +4966,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131989695</v>
+        <v>131989692</v>
       </c>
       <c r="B40" t="n">
         <v>91908</v>
@@ -4992,10 +5001,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566461</v>
+        <v>566516</v>
       </c>
       <c r="R40" t="n">
-        <v>6679189</v>
+        <v>6679071</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5027,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5037,7 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5064,54 +5073,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131989721</v>
+        <v>131989695</v>
       </c>
       <c r="B41" t="n">
-        <v>99116</v>
+        <v>91908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566585</v>
+        <v>566461</v>
       </c>
       <c r="R41" t="n">
-        <v>6679241</v>
+        <v>6679189</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131989734</v>
+        <v>131989685</v>
       </c>
       <c r="B2" t="n">
-        <v>99116</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566886</v>
+        <v>566683</v>
       </c>
       <c r="R2" t="n">
-        <v>6679158</v>
+        <v>6679245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131989685</v>
+        <v>131989734</v>
       </c>
       <c r="B3" t="n">
-        <v>91871</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566683</v>
+        <v>566886</v>
       </c>
       <c r="R3" t="n">
-        <v>6679245</v>
+        <v>6679158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,50 +898,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131989698</v>
+        <v>131989697</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566601</v>
+        <v>566627</v>
       </c>
       <c r="R4" t="n">
-        <v>6679232</v>
+        <v>6679348</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,45 +1005,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131989697</v>
+        <v>131989698</v>
       </c>
       <c r="B5" t="n">
-        <v>91908</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566627</v>
+        <v>566601</v>
       </c>
       <c r="R5" t="n">
-        <v>6679348</v>
+        <v>6679232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1120,7 @@
         <v>131989726</v>
       </c>
       <c r="B6" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>131989716</v>
       </c>
       <c r="B7" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>131989688</v>
       </c>
       <c r="B8" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131989730</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>131989728</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>131989719</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,38 +1804,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989703</v>
+        <v>131989712</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1844,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566786</v>
+        <v>566598</v>
       </c>
       <c r="R12" t="n">
-        <v>6679271</v>
+        <v>6679291</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989712</v>
+        <v>131989718</v>
       </c>
       <c r="B13" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,7 +1950,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1960,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566598</v>
+        <v>566526</v>
       </c>
       <c r="R13" t="n">
-        <v>6679291</v>
+        <v>6679221</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1999,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2009,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,42 +2036,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989718</v>
+        <v>131989703</v>
       </c>
       <c r="B14" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566526</v>
+        <v>566786</v>
       </c>
       <c r="R14" t="n">
-        <v>6679221</v>
+        <v>6679271</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,54 +2148,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131989715</v>
+        <v>131989696</v>
       </c>
       <c r="B15" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566602</v>
+        <v>566485</v>
       </c>
       <c r="R15" t="n">
-        <v>6679219</v>
+        <v>6679257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,7 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131989720</v>
+        <v>131989715</v>
       </c>
       <c r="B16" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,7 +2285,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2308,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566600</v>
+        <v>566602</v>
       </c>
       <c r="R16" t="n">
-        <v>6679228</v>
+        <v>6679219</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2344,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131989731</v>
+        <v>131989720</v>
       </c>
       <c r="B17" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2401,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2424,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566563</v>
+        <v>566600</v>
       </c>
       <c r="R17" t="n">
-        <v>6679314</v>
+        <v>6679228</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,45 +2487,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131989696</v>
+        <v>131989731</v>
       </c>
       <c r="B18" t="n">
-        <v>91908</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566485</v>
+        <v>566563</v>
       </c>
       <c r="R18" t="n">
-        <v>6679257</v>
+        <v>6679314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,7 +2606,7 @@
         <v>131989689</v>
       </c>
       <c r="B19" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131989735</v>
+        <v>131989722</v>
       </c>
       <c r="B20" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566580</v>
+        <v>566570</v>
       </c>
       <c r="R20" t="n">
-        <v>6679241</v>
+        <v>6679277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131989722</v>
+        <v>131989735</v>
       </c>
       <c r="B21" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566570</v>
+        <v>566580</v>
       </c>
       <c r="R21" t="n">
-        <v>6679277</v>
+        <v>6679241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3286,7 +3286,7 @@
         <v>131989725</v>
       </c>
       <c r="B25" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>131989686</v>
       </c>
       <c r="B26" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3506,54 +3506,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989717</v>
+        <v>131989687</v>
       </c>
       <c r="B27" t="n">
-        <v>99116</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566525</v>
+        <v>566505</v>
       </c>
       <c r="R27" t="n">
-        <v>6679095</v>
+        <v>6679080</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3585,7 +3576,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3586,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3622,32 +3613,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989687</v>
+        <v>131989691</v>
       </c>
       <c r="B28" t="n">
-        <v>91871</v>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3657,10 +3648,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566505</v>
+        <v>566556</v>
       </c>
       <c r="R28" t="n">
-        <v>6679080</v>
+        <v>6679090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3692,7 +3683,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3693,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,45 +3720,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989691</v>
+        <v>131989717</v>
       </c>
       <c r="B29" t="n">
-        <v>91908</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566556</v>
+        <v>566525</v>
       </c>
       <c r="R29" t="n">
-        <v>6679090</v>
+        <v>6679095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,7 +3839,7 @@
         <v>131989713</v>
       </c>
       <c r="B30" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>131989709</v>
       </c>
       <c r="B31" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131989710</v>
       </c>
       <c r="B32" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>131989690</v>
       </c>
       <c r="B33" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>131989714</v>
       </c>
       <c r="B35" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>131989729</v>
       </c>
       <c r="B36" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>131989732</v>
       </c>
       <c r="B37" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>131989721</v>
       </c>
       <c r="B38" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131989693</v>
+        <v>131989695</v>
       </c>
       <c r="B39" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566484</v>
+        <v>566461</v>
       </c>
       <c r="R39" t="n">
-        <v>6679089</v>
+        <v>6679189</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4969,7 +4969,7 @@
         <v>131989692</v>
       </c>
       <c r="B40" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131989695</v>
+        <v>131989693</v>
       </c>
       <c r="B41" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566461</v>
+        <v>566484</v>
       </c>
       <c r="R41" t="n">
-        <v>6679189</v>
+        <v>6679089</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5295,7 +5295,7 @@
         <v>131989724</v>
       </c>
       <c r="B43" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -1804,42 +1804,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989712</v>
+        <v>131989703</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1848,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566598</v>
+        <v>566786</v>
       </c>
       <c r="R12" t="n">
-        <v>6679291</v>
+        <v>6679271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989718</v>
+        <v>131989712</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1950,7 +1946,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1964,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566526</v>
+        <v>566598</v>
       </c>
       <c r="R13" t="n">
-        <v>6679221</v>
+        <v>6679291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,38 +2032,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989703</v>
+        <v>131989718</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566786</v>
+        <v>566526</v>
       </c>
       <c r="R14" t="n">
-        <v>6679271</v>
+        <v>6679221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4278,38 +4278,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989744</v>
+        <v>131989714</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4318,10 +4327,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566439</v>
+        <v>566771</v>
       </c>
       <c r="R34" t="n">
-        <v>6679145</v>
+        <v>6679247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4353,7 +4362,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4363,7 +4372,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,7 +4399,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989714</v>
+        <v>131989729</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4420,7 +4429,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4428,21 +4437,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566771</v>
+        <v>566608</v>
       </c>
       <c r="R35" t="n">
-        <v>6679247</v>
+        <v>6679223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4484,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,42 +4515,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989729</v>
+        <v>131989744</v>
       </c>
       <c r="B36" t="n">
-        <v>99118</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566608</v>
+        <v>566439</v>
       </c>
       <c r="R36" t="n">
-        <v>6679223</v>
+        <v>6679145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5180,38 +5180,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131989743</v>
+        <v>131989724</v>
       </c>
       <c r="B42" t="n">
-        <v>5179</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5220,10 +5224,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566470</v>
+        <v>566527</v>
       </c>
       <c r="R42" t="n">
-        <v>6679099</v>
+        <v>6679247</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5255,7 +5259,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,7 +5269,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5292,42 +5296,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131989724</v>
+        <v>131989743</v>
       </c>
       <c r="B43" t="n">
-        <v>99118</v>
+        <v>5179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566527</v>
+        <v>566470</v>
       </c>
       <c r="R43" t="n">
-        <v>6679247</v>
+        <v>6679099</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131989685</v>
+        <v>131989690</v>
       </c>
       <c r="B2" t="n">
-        <v>91872</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566683</v>
+        <v>566533</v>
       </c>
       <c r="R2" t="n">
-        <v>6679245</v>
+        <v>6679097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131989734</v>
+        <v>131989691</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566886</v>
+        <v>566556</v>
       </c>
       <c r="R3" t="n">
-        <v>6679158</v>
+        <v>6679090</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131989697</v>
+        <v>131989692</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566627</v>
+        <v>566516</v>
       </c>
       <c r="R4" t="n">
-        <v>6679348</v>
+        <v>6679071</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131989698</v>
+        <v>131989693</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566601</v>
+        <v>566484</v>
       </c>
       <c r="R5" t="n">
-        <v>6679232</v>
+        <v>6679089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,54 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131989726</v>
+        <v>131989695</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566577</v>
+        <v>566461</v>
       </c>
       <c r="R6" t="n">
-        <v>6679273</v>
+        <v>6679189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,54 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131989716</v>
+        <v>131989696</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566574</v>
+        <v>566485</v>
       </c>
       <c r="R7" t="n">
-        <v>6679277</v>
+        <v>6679257</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131989688</v>
+        <v>131989697</v>
       </c>
       <c r="B8" t="n">
-        <v>91872</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566662</v>
+        <v>566627</v>
       </c>
       <c r="R8" t="n">
-        <v>6679349</v>
+        <v>6679348</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131989730</v>
+        <v>131989689</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>92318</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,43 +1435,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566655</v>
+        <v>566483</v>
       </c>
       <c r="R9" t="n">
-        <v>6679324</v>
+        <v>6679261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,54 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131989728</v>
+        <v>131989685</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>91937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566628</v>
+        <v>566683</v>
       </c>
       <c r="R10" t="n">
-        <v>6679344</v>
+        <v>6679245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,54 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131989719</v>
+        <v>131989686</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>91937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566870</v>
+        <v>566607</v>
       </c>
       <c r="R11" t="n">
-        <v>6679162</v>
+        <v>6679234</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,50 +1745,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131989703</v>
+        <v>131989687</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>91937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566786</v>
+        <v>566505</v>
       </c>
       <c r="R12" t="n">
-        <v>6679271</v>
+        <v>6679080</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,54 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131989712</v>
+        <v>131989688</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566598</v>
+        <v>566662</v>
       </c>
       <c r="R13" t="n">
-        <v>6679291</v>
+        <v>6679349</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,42 +1959,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131989718</v>
+        <v>131989703</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566526</v>
+        <v>566786</v>
       </c>
       <c r="R14" t="n">
-        <v>6679221</v>
+        <v>6679271</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,45 +2071,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131989696</v>
+        <v>131989704</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566485</v>
+        <v>566583</v>
       </c>
       <c r="R15" t="n">
-        <v>6679257</v>
+        <v>6679080</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2228,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,42 +2183,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131989715</v>
+        <v>131989705</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2299,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566602</v>
+        <v>566588</v>
       </c>
       <c r="R16" t="n">
-        <v>6679219</v>
+        <v>6679099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,42 +2295,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131989720</v>
+        <v>131989698</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>4776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2415,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566600</v>
+        <v>566601</v>
       </c>
       <c r="R17" t="n">
-        <v>6679228</v>
+        <v>6679232</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,42 +2407,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131989731</v>
+        <v>131989743</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>5181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2531,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566563</v>
+        <v>566470</v>
       </c>
       <c r="R18" t="n">
-        <v>6679314</v>
+        <v>6679099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2482,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2492,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,45 +2519,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131989689</v>
+        <v>131989744</v>
       </c>
       <c r="B19" t="n">
-        <v>92281</v>
+        <v>5181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566483</v>
+        <v>566439</v>
       </c>
       <c r="R19" t="n">
-        <v>6679261</v>
+        <v>6679145</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,42 +2631,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131989722</v>
+        <v>131989700</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2754,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566570</v>
+        <v>566496</v>
       </c>
       <c r="R20" t="n">
-        <v>6679277</v>
+        <v>6679281</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2799,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,42 +2748,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131989735</v>
+        <v>131989701</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2870,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566580</v>
+        <v>566614</v>
       </c>
       <c r="R21" t="n">
-        <v>6679241</v>
+        <v>6679286</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,7 +2863,7 @@
         <v>131989742</v>
       </c>
       <c r="B22" t="n">
-        <v>8444</v>
+        <v>8449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,43 +2972,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131989700</v>
+        <v>131989712</v>
       </c>
       <c r="B23" t="n">
-        <v>58114</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3099,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566496</v>
+        <v>566598</v>
       </c>
       <c r="R23" t="n">
-        <v>6679281</v>
+        <v>6679291</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,7 +3051,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3144,7 +3061,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3171,38 +3088,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131989701</v>
+        <v>131989713</v>
       </c>
       <c r="B24" t="n">
-        <v>58114</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3211,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566614</v>
+        <v>566531</v>
       </c>
       <c r="R24" t="n">
-        <v>6679286</v>
+        <v>6679247</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3246,7 +3167,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,7 +3177,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3283,10 +3204,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131989725</v>
+        <v>131989714</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3234,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3321,16 +3242,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566869</v>
+        <v>566771</v>
       </c>
       <c r="R25" t="n">
-        <v>6679157</v>
+        <v>6679247</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3362,7 +3288,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3298,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,45 +3325,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131989686</v>
+        <v>131989715</v>
       </c>
       <c r="B26" t="n">
-        <v>91872</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566607</v>
+        <v>566602</v>
       </c>
       <c r="R26" t="n">
-        <v>6679234</v>
+        <v>6679219</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3469,7 +3404,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3479,7 +3414,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3506,45 +3441,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131989687</v>
+        <v>131989716</v>
       </c>
       <c r="B27" t="n">
-        <v>91872</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566505</v>
+        <v>566574</v>
       </c>
       <c r="R27" t="n">
-        <v>6679080</v>
+        <v>6679277</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3520,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3530,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,45 +3557,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131989691</v>
+        <v>131989717</v>
       </c>
       <c r="B28" t="n">
-        <v>91909</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566556</v>
+        <v>566525</v>
       </c>
       <c r="R28" t="n">
-        <v>6679090</v>
+        <v>6679095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3683,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3693,7 +3646,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3720,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131989717</v>
+        <v>131989718</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3750,7 +3703,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3764,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566525</v>
+        <v>566526</v>
       </c>
       <c r="R29" t="n">
-        <v>6679095</v>
+        <v>6679221</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,10 +3789,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131989713</v>
+        <v>131989719</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3866,7 +3819,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3880,10 +3833,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566531</v>
+        <v>566870</v>
       </c>
       <c r="R30" t="n">
-        <v>6679247</v>
+        <v>6679162</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3915,7 +3868,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3925,7 +3878,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,45 +3905,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131989709</v>
+        <v>131989720</v>
       </c>
       <c r="B31" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566652</v>
+        <v>566600</v>
       </c>
       <c r="R31" t="n">
-        <v>6679329</v>
+        <v>6679228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +3984,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,12 +3994,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>I gammal kolbotten</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,45 +4021,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131989710</v>
+        <v>131989721</v>
       </c>
       <c r="B32" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566626</v>
+        <v>566585</v>
       </c>
       <c r="R32" t="n">
-        <v>6679348</v>
+        <v>6679241</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4134,7 +4100,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4144,7 +4110,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,45 +4137,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131989690</v>
+        <v>131989722</v>
       </c>
       <c r="B33" t="n">
-        <v>91909</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566533</v>
+        <v>566570</v>
       </c>
       <c r="R33" t="n">
-        <v>6679097</v>
+        <v>6679277</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4216,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4226,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,10 +4253,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131989714</v>
+        <v>131989724</v>
       </c>
       <c r="B34" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4308,7 +4283,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4316,18 +4291,13 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566771</v>
+        <v>566527</v>
       </c>
       <c r="R34" t="n">
         <v>6679247</v>
@@ -4362,7 +4332,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4372,7 +4342,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4399,10 +4369,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131989729</v>
+        <v>131989725</v>
       </c>
       <c r="B35" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4399,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4443,10 +4413,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566608</v>
+        <v>566869</v>
       </c>
       <c r="R35" t="n">
-        <v>6679223</v>
+        <v>6679157</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4448,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4458,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,38 +4485,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131989744</v>
+        <v>131989726</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>99195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4555,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566439</v>
+        <v>566577</v>
       </c>
       <c r="R36" t="n">
-        <v>6679145</v>
+        <v>6679273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4564,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4574,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4627,10 +4601,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131989732</v>
+        <v>131989728</v>
       </c>
       <c r="B37" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,7 +4631,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4671,10 +4645,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566509</v>
+        <v>566628</v>
       </c>
       <c r="R37" t="n">
-        <v>6679211</v>
+        <v>6679344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4706,7 +4680,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4716,7 +4690,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4743,10 +4717,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131989721</v>
+        <v>131989729</v>
       </c>
       <c r="B38" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4747,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4787,10 +4761,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566585</v>
+        <v>566608</v>
       </c>
       <c r="R38" t="n">
-        <v>6679241</v>
+        <v>6679223</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4822,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4806,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,45 +4833,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131989695</v>
+        <v>131989730</v>
       </c>
       <c r="B39" t="n">
-        <v>91909</v>
+        <v>99195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566461</v>
+        <v>566655</v>
       </c>
       <c r="R39" t="n">
-        <v>6679189</v>
+        <v>6679324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4929,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4939,7 +4922,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4966,45 +4949,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131989692</v>
+        <v>131989731</v>
       </c>
       <c r="B40" t="n">
-        <v>91909</v>
+        <v>99195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566516</v>
+        <v>566563</v>
       </c>
       <c r="R40" t="n">
-        <v>6679071</v>
+        <v>6679314</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5036,7 +5028,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5038,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5073,45 +5065,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131989693</v>
+        <v>131989732</v>
       </c>
       <c r="B41" t="n">
-        <v>91909</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rotfallsberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566484</v>
+        <v>566509</v>
       </c>
       <c r="R41" t="n">
-        <v>6679089</v>
+        <v>6679211</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5143,7 +5144,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5154,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5180,10 +5181,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131989724</v>
+        <v>131989733</v>
       </c>
       <c r="B42" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,7 +5211,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5224,10 +5225,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566527</v>
+        <v>566589</v>
       </c>
       <c r="R42" t="n">
-        <v>6679247</v>
+        <v>6679161</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5259,7 +5260,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5269,7 +5270,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5296,38 +5297,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131989743</v>
+        <v>131989734</v>
       </c>
       <c r="B43" t="n">
-        <v>5179</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5336,10 +5341,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566470</v>
+        <v>566886</v>
       </c>
       <c r="R43" t="n">
-        <v>6679099</v>
+        <v>6679158</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5376,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5381,7 +5386,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5405,6 +5410,341 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131989735</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rotfallsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>566580</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6679241</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131989709</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rotfallsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>566652</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6679329</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I gammal kolbotten</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131989710</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Rotfallsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>566626</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6679348</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10669-2026 artfynd.xlsx
+++ b/artfynd/A 10669-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989692</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989693</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989695</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989696</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989697</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989689</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989685</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989686</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989687</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989688</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989703</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989704</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989705</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989698</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2516,6 +2601,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989743</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2628,6 +2718,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989744</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2745,6 +2840,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989700</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2857,6 +2957,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989701</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2969,6 +3074,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989742</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3085,6 +3195,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989712</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3201,6 +3316,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989713</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3322,6 +3442,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989714</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3438,6 +3563,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989715</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3554,6 +3684,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989716</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3670,6 +3805,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989717</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3786,6 +3926,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989718</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3902,6 +4047,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989719</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4018,6 +4168,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989720</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4134,6 +4289,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989721</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4250,6 +4410,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989722</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4366,6 +4531,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989724</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4482,6 +4652,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989725</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4598,6 +4773,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989726</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4714,6 +4894,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989728</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4830,6 +5015,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989729</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4946,6 +5136,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989730</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5062,6 +5257,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989731</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5178,6 +5378,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989732</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5294,6 +5499,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989733</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5410,6 +5620,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989734</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5526,6 +5741,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989735</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5638,6 +5858,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989709</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5745,8 +5970,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>